--- a/ig/DM_FINESS_New/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2315" uniqueCount="2313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2343" uniqueCount="2341">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250131120000</t>
+    <t>20250425120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T12:00:00+01:00</t>
+    <t>2025-04-25T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -654,7 +654,7 @@
     <t>0169</t>
   </si>
   <si>
-    <t>Détection du dopage</t>
+    <t>Dépistage et prise en charge du dopage</t>
   </si>
   <si>
     <t>0172</t>
@@ -1026,7 +1026,7 @@
     <t>0266</t>
   </si>
   <si>
-    <t>Interruption thérapeutique de grossesse</t>
+    <t>Interruption de grossesse pour motif médical (IMG/ITG)</t>
   </si>
   <si>
     <t>0267</t>
@@ -2724,7 +2724,7 @@
     <t>0723</t>
   </si>
   <si>
-    <t>Accompagnement à la réinsertion professionnelle</t>
+    <t>Accompagnement à l'insertion ou la réinsertion professionnelle</t>
   </si>
   <si>
     <t>0724</t>
@@ -4914,7 +4914,7 @@
     <t>1140</t>
   </si>
   <si>
-    <t>Bilan radiologique chez les patients différents (handicaps physiques, psychiques, claustrophobie, …)</t>
+    <t>Bilan radiologique avec prise en charge adaptée (handicaps physiques, psychiques, claustrophobie, …)</t>
   </si>
   <si>
     <t>1141</t>
@@ -6765,12 +6765,6 @@
     <t>Délivrance de certificats spécifiques pour les sportifs en situation de Handicap</t>
   </si>
   <si>
-    <t>1466</t>
-  </si>
-  <si>
-    <t>Dépistage et prise en charge du dopage</t>
-  </si>
-  <si>
     <t>1467</t>
   </si>
   <si>
@@ -6825,12 +6819,6 @@
     <t>Analyse tridimensionnelle du mouvement, de la marche</t>
   </si>
   <si>
-    <t>1476</t>
-  </si>
-  <si>
-    <t>Accès direct Infirmier en Pratique Avancée (IPA), kinésithérapeute, orthophoniste</t>
-  </si>
-  <si>
     <t>1477</t>
   </si>
   <si>
@@ -6943,6 +6931,102 @@
   </si>
   <si>
     <t>HandiBloc</t>
+  </si>
+  <si>
+    <t>1496</t>
+  </si>
+  <si>
+    <t>Accompagnement des troubles de l'écriture</t>
+  </si>
+  <si>
+    <t>1497</t>
+  </si>
+  <si>
+    <t>Accompagnement ergothérapique à l'accès aux nouvelles technologies</t>
+  </si>
+  <si>
+    <t>1498</t>
+  </si>
+  <si>
+    <t>Accompagnement ergothérapique auprès des proches aidants (proches et professionnels) : apprentissage de techniques d'accompagnement</t>
+  </si>
+  <si>
+    <t>1499</t>
+  </si>
+  <si>
+    <t>Accompagnement ergothérapique dans le cadre de déficiences visuelles</t>
+  </si>
+  <si>
+    <t>1500</t>
+  </si>
+  <si>
+    <t>Accompagnement ergothérapique dans le cadre de maladies neuro-évolutives (SLA, SEP, Parkinson, Alzheimer, PNM)</t>
+  </si>
+  <si>
+    <t>1501</t>
+  </si>
+  <si>
+    <t>Accompagnement ergothérapique dans le cadre de particularités sensorielles (TND)</t>
+  </si>
+  <si>
+    <t>1502</t>
+  </si>
+  <si>
+    <t>Accompagnement ergothérapique dans le cadre de pathologies neurologiques (AVC, TCE)</t>
+  </si>
+  <si>
+    <t>1503</t>
+  </si>
+  <si>
+    <t>Accompagnement ergothérapique de rééducation/réadaptation en situation de vie quotidienne post-hospitalisation (RAD)</t>
+  </si>
+  <si>
+    <t>1504</t>
+  </si>
+  <si>
+    <t>Accompagnement ergothérapique des troubles alimentaires</t>
+  </si>
+  <si>
+    <t>1505</t>
+  </si>
+  <si>
+    <t>Accompagnement ergothérapique pour la prévention de la chute et ses conséquences : désadaptation psychomotrice</t>
+  </si>
+  <si>
+    <t>1506</t>
+  </si>
+  <si>
+    <t>Evaluation et accompagnement à la mise en place de communication augmentative-alternative</t>
+  </si>
+  <si>
+    <t>1507</t>
+  </si>
+  <si>
+    <t>Programme de prévention primaire ergothérapique « Bien vieillir » (TaPasS)</t>
+  </si>
+  <si>
+    <t>1508</t>
+  </si>
+  <si>
+    <t>Accompagnement ergothérapique en milieu scolaire</t>
+  </si>
+  <si>
+    <t>1509</t>
+  </si>
+  <si>
+    <t>Accompagnement ergothérapique en réhabilitation psycho-sociale</t>
+  </si>
+  <si>
+    <t>1510</t>
+  </si>
+  <si>
+    <t>Evaluation et accompagnement ergothérapique au positionnement au fauteuil roulant (MCPAA) et positionnement au lit</t>
+  </si>
+  <si>
+    <t>1511</t>
+  </si>
+  <si>
+    <t>Accompagnement précoce des déficiences</t>
   </si>
   <si>
     <t/>
@@ -7205,7 +7289,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1145"/>
+  <dimension ref="A1:B1159"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -16361,15 +16445,127 @@
         <v>2310</v>
       </c>
       <c r="B1144" t="s" s="2">
-        <v>2310</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="s" s="2">
-        <v>2311</v>
+        <v>2312</v>
       </c>
       <c r="B1145" t="s" s="2">
-        <v>2312</v>
+        <v>2313</v>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="s" s="2">
+        <v>2314</v>
+      </c>
+      <c r="B1146" t="s" s="2">
+        <v>2315</v>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="s" s="2">
+        <v>2316</v>
+      </c>
+      <c r="B1147" t="s" s="2">
+        <v>2317</v>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="s" s="2">
+        <v>2318</v>
+      </c>
+      <c r="B1148" t="s" s="2">
+        <v>2319</v>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="s" s="2">
+        <v>2320</v>
+      </c>
+      <c r="B1149" t="s" s="2">
+        <v>2321</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="s" s="2">
+        <v>2322</v>
+      </c>
+      <c r="B1150" t="s" s="2">
+        <v>2323</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="s" s="2">
+        <v>2324</v>
+      </c>
+      <c r="B1151" t="s" s="2">
+        <v>2325</v>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="s" s="2">
+        <v>2326</v>
+      </c>
+      <c r="B1152" t="s" s="2">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="s" s="2">
+        <v>2328</v>
+      </c>
+      <c r="B1153" t="s" s="2">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="s" s="2">
+        <v>2330</v>
+      </c>
+      <c r="B1154" t="s" s="2">
+        <v>2331</v>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="s" s="2">
+        <v>2332</v>
+      </c>
+      <c r="B1155" t="s" s="2">
+        <v>2333</v>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="s" s="2">
+        <v>2334</v>
+      </c>
+      <c r="B1156" t="s" s="2">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="s" s="2">
+        <v>2336</v>
+      </c>
+      <c r="B1157" t="s" s="2">
+        <v>2337</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="s" s="2">
+        <v>2338</v>
+      </c>
+      <c r="B1158" t="s" s="2">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="s" s="2">
+        <v>2339</v>
+      </c>
+      <c r="B1159" t="s" s="2">
+        <v>2340</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2343" uniqueCount="2341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2397" uniqueCount="2395">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250425120000</t>
+    <t>20250625120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T12:00:00+01:00</t>
+    <t>2025-06-25T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1710,13 +1710,13 @@
     <t>0500</t>
   </si>
   <si>
-    <t>Vaccination antirabique (rage)</t>
+    <t>Vaccination antirabique (rage) post-exposition</t>
   </si>
   <si>
     <t>0501</t>
   </si>
   <si>
-    <t>Vaccinations internationales et conseils aux voyageurs (fièvre jaune, encéphalite…)</t>
+    <t>Vaccinations des voyageurs</t>
   </si>
   <si>
     <t>0503</t>
@@ -1743,12 +1743,6 @@
     <t>Acupuncture</t>
   </si>
   <si>
-    <t>0510</t>
-  </si>
-  <si>
-    <t>Dialyse péritonéale</t>
-  </si>
-  <si>
     <t>0512</t>
   </si>
   <si>
@@ -3693,6 +3687,18 @@
     <t>Drainage bronchique</t>
   </si>
   <si>
+    <t>0897</t>
+  </si>
+  <si>
+    <t>Drainage Vaccination épidémie Grippe</t>
+  </si>
+  <si>
+    <t>0898</t>
+  </si>
+  <si>
+    <t>Dépistage du diabète</t>
+  </si>
+  <si>
     <t>0909</t>
   </si>
   <si>
@@ -4164,7 +4170,7 @@
     <t>1013</t>
   </si>
   <si>
-    <t>Vaccination contre les maladies sexuellement transmissibles</t>
+    <t>Vaccination contre les infections sexuellement transmissible (IST)</t>
   </si>
   <si>
     <t>1014</t>
@@ -5520,13 +5526,13 @@
     <t>1244</t>
   </si>
   <si>
-    <t>Pose d'implants contraceptifs</t>
+    <t>Pose et retrait d’implants contraceptifs</t>
   </si>
   <si>
     <t>1245</t>
   </si>
   <si>
-    <t>Pose de DIU</t>
+    <t>Pose et retrait de stérilet (DIU/SIU)</t>
   </si>
   <si>
     <t>1246</t>
@@ -5760,7 +5766,7 @@
     <t>1284</t>
   </si>
   <si>
-    <t>Programme d'ETP labellisée - Insuffisance rénale, dialyse</t>
+    <t>Programme d'ETP labellisée - Maladie rénale chronique (MRC), dialyse</t>
   </si>
   <si>
     <t>1285</t>
@@ -6081,12 +6087,6 @@
     <t>Rééducation pelvi-périnéale</t>
   </si>
   <si>
-    <t>1342</t>
-  </si>
-  <si>
-    <t>Retrait de Dispositif Intra-Utérin (DIU) (stérilet) ou d'implant contraceptif</t>
-  </si>
-  <si>
     <t>1343</t>
   </si>
   <si>
@@ -7027,6 +7027,168 @@
   </si>
   <si>
     <t>Accompagnement précoce des déficiences</t>
+  </si>
+  <si>
+    <t>1512</t>
+  </si>
+  <si>
+    <t>Consultation spécialisée en allaitement</t>
+  </si>
+  <si>
+    <t>1513</t>
+  </si>
+  <si>
+    <t>Consultations néonatales pédiatriques</t>
+  </si>
+  <si>
+    <t>1514</t>
+  </si>
+  <si>
+    <t>Dialyse longue nocturne</t>
+  </si>
+  <si>
+    <t>1515</t>
+  </si>
+  <si>
+    <t>Diathermie et électrothérapie combinées en soins pelvi-périnéaux</t>
+  </si>
+  <si>
+    <t>1516</t>
+  </si>
+  <si>
+    <t>Évaluation et adaptation diététique de nutrition artificielle</t>
+  </si>
+  <si>
+    <t>1517</t>
+  </si>
+  <si>
+    <t>Parcours surpoids et obésité pédiatrique « Mission : Retrouve ton Cap »</t>
+  </si>
+  <si>
+    <t>1518</t>
+  </si>
+  <si>
+    <t>Participation au dispositif HandiGynéco</t>
+  </si>
+  <si>
+    <t>1519</t>
+  </si>
+  <si>
+    <t>Séance de préparation à la naissance et à la parentalité individuelle</t>
+  </si>
+  <si>
+    <t>1520</t>
+  </si>
+  <si>
+    <t>Soin diététique et nutritionnel adulte pendant et après les traitements oncologiques</t>
+  </si>
+  <si>
+    <t>1521</t>
+  </si>
+  <si>
+    <t>Soin diététique et nutritionnel des alimentations pauvres en FODMAPs</t>
+  </si>
+  <si>
+    <t>1522</t>
+  </si>
+  <si>
+    <t>Soin diététique et nutritionnel des allergies alimentaires</t>
+  </si>
+  <si>
+    <t>1523</t>
+  </si>
+  <si>
+    <t>Soin diététique et nutritionnel des personnes en situation de handicap</t>
+  </si>
+  <si>
+    <t>1524</t>
+  </si>
+  <si>
+    <t>Soin diététique et nutritionnel des Troubles Alimentaires Pédiatriques (TAP)</t>
+  </si>
+  <si>
+    <t>1525</t>
+  </si>
+  <si>
+    <t>Soin diététique et nutritionnel des troubles de la déglutition ou dysphagies</t>
+  </si>
+  <si>
+    <t>1526</t>
+  </si>
+  <si>
+    <t>Soin diététique et nutritionnel pédiatrique pendant et après les traitements oncologiques</t>
+  </si>
+  <si>
+    <t>1527</t>
+  </si>
+  <si>
+    <t>Soin diététique et nutritionnel pour la gestion des troubles hormonaux (hypothyroïdie, SOPK, endométriose)</t>
+  </si>
+  <si>
+    <t>1528</t>
+  </si>
+  <si>
+    <t>Soin diététique et nutritionnel des diabètes</t>
+  </si>
+  <si>
+    <t>1529</t>
+  </si>
+  <si>
+    <t>Soins gynécologiques pour personnes en situation de handicap</t>
+  </si>
+  <si>
+    <t>1530</t>
+  </si>
+  <si>
+    <t>Suivi post-accouchement à domicile</t>
+  </si>
+  <si>
+    <t>1531</t>
+  </si>
+  <si>
+    <t>Suivi staturopondéral des nourrissons</t>
+  </si>
+  <si>
+    <t>1532</t>
+  </si>
+  <si>
+    <t>Surveillance d'ictère néonatal par mesure transcutanée</t>
+  </si>
+  <si>
+    <t>1533</t>
+  </si>
+  <si>
+    <t>Test de Guthrie hors établissement (test néonatal du buvard)</t>
+  </si>
+  <si>
+    <t>1534</t>
+  </si>
+  <si>
+    <t>Vaccination contre la tuberculose</t>
+  </si>
+  <si>
+    <t>1535</t>
+  </si>
+  <si>
+    <t>Vaccination du calendrier vaccinal de l’adolescent et de l’adulte</t>
+  </si>
+  <si>
+    <t>1536</t>
+  </si>
+  <si>
+    <t>Vaccination du calendrier vaccinal du jeune enfant (0-12 ans)</t>
+  </si>
+  <si>
+    <t>1537</t>
+  </si>
+  <si>
+    <t>Vaccination du calendrier vaccinal du sénior</t>
+  </si>
+  <si>
+    <t>1538</t>
+  </si>
+  <si>
+    <t>Vaccination épidémie Covid</t>
   </si>
   <si>
     <t/>
@@ -7289,7 +7451,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1159"/>
+  <dimension ref="A1:B1186"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -16557,15 +16719,231 @@
         <v>2338</v>
       </c>
       <c r="B1158" t="s" s="2">
-        <v>2338</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="s" s="2">
-        <v>2339</v>
+        <v>2340</v>
       </c>
       <c r="B1159" t="s" s="2">
-        <v>2340</v>
+        <v>2341</v>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="s" s="2">
+        <v>2342</v>
+      </c>
+      <c r="B1160" t="s" s="2">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="s" s="2">
+        <v>2344</v>
+      </c>
+      <c r="B1161" t="s" s="2">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="s" s="2">
+        <v>2346</v>
+      </c>
+      <c r="B1162" t="s" s="2">
+        <v>2347</v>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="s" s="2">
+        <v>2348</v>
+      </c>
+      <c r="B1163" t="s" s="2">
+        <v>2349</v>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="s" s="2">
+        <v>2350</v>
+      </c>
+      <c r="B1164" t="s" s="2">
+        <v>2351</v>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="s" s="2">
+        <v>2352</v>
+      </c>
+      <c r="B1165" t="s" s="2">
+        <v>2353</v>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="s" s="2">
+        <v>2354</v>
+      </c>
+      <c r="B1166" t="s" s="2">
+        <v>2355</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="s" s="2">
+        <v>2356</v>
+      </c>
+      <c r="B1167" t="s" s="2">
+        <v>2357</v>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="s" s="2">
+        <v>2358</v>
+      </c>
+      <c r="B1168" t="s" s="2">
+        <v>2359</v>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="s" s="2">
+        <v>2360</v>
+      </c>
+      <c r="B1169" t="s" s="2">
+        <v>2361</v>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="s" s="2">
+        <v>2362</v>
+      </c>
+      <c r="B1170" t="s" s="2">
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="s" s="2">
+        <v>2364</v>
+      </c>
+      <c r="B1171" t="s" s="2">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="s" s="2">
+        <v>2366</v>
+      </c>
+      <c r="B1172" t="s" s="2">
+        <v>2367</v>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="s" s="2">
+        <v>2368</v>
+      </c>
+      <c r="B1173" t="s" s="2">
+        <v>2369</v>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="s" s="2">
+        <v>2370</v>
+      </c>
+      <c r="B1174" t="s" s="2">
+        <v>2371</v>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="s" s="2">
+        <v>2372</v>
+      </c>
+      <c r="B1175" t="s" s="2">
+        <v>2373</v>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="s" s="2">
+        <v>2374</v>
+      </c>
+      <c r="B1176" t="s" s="2">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="s" s="2">
+        <v>2376</v>
+      </c>
+      <c r="B1177" t="s" s="2">
+        <v>2377</v>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="s" s="2">
+        <v>2378</v>
+      </c>
+      <c r="B1178" t="s" s="2">
+        <v>2379</v>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="s" s="2">
+        <v>2380</v>
+      </c>
+      <c r="B1179" t="s" s="2">
+        <v>2381</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="s" s="2">
+        <v>2382</v>
+      </c>
+      <c r="B1180" t="s" s="2">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="s" s="2">
+        <v>2384</v>
+      </c>
+      <c r="B1181" t="s" s="2">
+        <v>2385</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="s" s="2">
+        <v>2386</v>
+      </c>
+      <c r="B1182" t="s" s="2">
+        <v>2387</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="s" s="2">
+        <v>2388</v>
+      </c>
+      <c r="B1183" t="s" s="2">
+        <v>2389</v>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="s" s="2">
+        <v>2390</v>
+      </c>
+      <c r="B1184" t="s" s="2">
+        <v>2391</v>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="s" s="2">
+        <v>2392</v>
+      </c>
+      <c r="B1185" t="s" s="2">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="s" s="2">
+        <v>2393</v>
+      </c>
+      <c r="B1186" t="s" s="2">
+        <v>2394</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2399" uniqueCount="2397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="2409">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250625120000</t>
+    <t>20250919120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-25T12:00:00+01:00</t>
+    <t>2025-09-19T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -291,12 +291,6 @@
     <t>Chirurgie carcinologique gynécologique</t>
   </si>
   <si>
-    <t>0055</t>
-  </si>
-  <si>
-    <t>Chirurgie carcinologique maxillo-faciale et stomatologique</t>
-  </si>
-  <si>
     <t>0056</t>
   </si>
   <si>
@@ -1338,7 +1332,7 @@
     <t>0384</t>
   </si>
   <si>
-    <t>Prélèvement d'organes à coeur battant</t>
+    <t>Prélèvement d'organes à coeur battant (mort cérébrale)</t>
   </si>
   <si>
     <t>0385</t>
@@ -1413,12 +1407,6 @@
     <t>Rééducation basse vision</t>
   </si>
   <si>
-    <t>0413</t>
-  </si>
-  <si>
-    <t>Rééducation orthoptique</t>
-  </si>
-  <si>
     <t>0415</t>
   </si>
   <si>
@@ -1533,12 +1521,6 @@
     <t>Scintigraphie SPECT-CT</t>
   </si>
   <si>
-    <t>0440</t>
-  </si>
-  <si>
-    <t>Soins odontologiques sous anesthésie générale (AG)</t>
-  </si>
-  <si>
     <t>0441</t>
   </si>
   <si>
@@ -2763,12 +2745,6 @@
     <t>Suivi de grossesse à risque</t>
   </si>
   <si>
-    <t>0731</t>
-  </si>
-  <si>
-    <t>Surveillance du nouveau-né à risque</t>
-  </si>
-  <si>
     <t>0732</t>
   </si>
   <si>
@@ -3198,7 +3174,7 @@
     <t>0810</t>
   </si>
   <si>
-    <t>Préparation à la naissance et à la parentalité</t>
+    <t>Séance de préparation à la naissance et à la parentalité en groupe</t>
   </si>
   <si>
     <t>0812</t>
@@ -3669,12 +3645,6 @@
     <t>Réadaptation vésico-sphinctérienne</t>
   </si>
   <si>
-    <t>0893</t>
-  </si>
-  <si>
-    <t>Réadaptation des fonctions sexuelles et de la reproduction</t>
-  </si>
-  <si>
     <t>0894</t>
   </si>
   <si>
@@ -3846,7 +3816,7 @@
     <t>0932</t>
   </si>
   <si>
-    <t>Tests Rapides d'Orientation Diagnostique (TROD)</t>
+    <t>Test Rapide d’Orientation Diagnostique (TROD) VIH / Hépatite B / Hépatite C</t>
   </si>
   <si>
     <t>0958</t>
@@ -4761,12 +4731,6 @@
     <t>Test au baclofène intrathécal</t>
   </si>
   <si>
-    <t>1113</t>
-  </si>
-  <si>
-    <t>Thérapie manuelle</t>
-  </si>
-  <si>
     <t>1114</t>
   </si>
   <si>
@@ -6870,7 +6834,7 @@
     <t>1484</t>
   </si>
   <si>
-    <t>Télésurveillance médicale de l'insuffisance rénale</t>
+    <t>Télésurveillance médicale de la maladie rénale chronique (MRC)</t>
   </si>
   <si>
     <t>1485</t>
@@ -7195,6 +7159,78 @@
   </si>
   <si>
     <t>Vaccination épidémie Covid</t>
+  </si>
+  <si>
+    <t>1539</t>
+  </si>
+  <si>
+    <t>Test Rapide d’Orientation Diagnostique (TROD) Covid-19</t>
+  </si>
+  <si>
+    <t>1540</t>
+  </si>
+  <si>
+    <t>Test Rapide d’Orientation Diagnostique (TROD) Grippe</t>
+  </si>
+  <si>
+    <t>1541</t>
+  </si>
+  <si>
+    <t>Test Rapide d’Orientation Diagnostique (TROD) Virus respiratoire syncytial (VRS)</t>
+  </si>
+  <si>
+    <t>1542</t>
+  </si>
+  <si>
+    <t>Test Rapide d’Orientation Diagnostique (TROD) Angine</t>
+  </si>
+  <si>
+    <t>1543</t>
+  </si>
+  <si>
+    <t>Test Rapide d’Orientation Diagnostique (TROD) Syphilis</t>
+  </si>
+  <si>
+    <t>1544</t>
+  </si>
+  <si>
+    <t>Test Rapide d’Orientation Diagnostique (TROD) Cystite</t>
+  </si>
+  <si>
+    <t>1545</t>
+  </si>
+  <si>
+    <t>Chirurgie de l’allongement osseux</t>
+  </si>
+  <si>
+    <t>1546</t>
+  </si>
+  <si>
+    <t>Correction des malformations congénitales de la main</t>
+  </si>
+  <si>
+    <t>1547</t>
+  </si>
+  <si>
+    <t>Accueil saisonnier possible</t>
+  </si>
+  <si>
+    <t>1548</t>
+  </si>
+  <si>
+    <t>Accueil saisonnier uniquement</t>
+  </si>
+  <si>
+    <t>1549</t>
+  </si>
+  <si>
+    <t>Autodialyse simple</t>
+  </si>
+  <si>
+    <t>1550</t>
+  </si>
+  <si>
+    <t>Autodialyse assistée</t>
   </si>
   <si>
     <t/>
@@ -7465,7 +7501,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1186"/>
+  <dimension ref="A1:B1192"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -16949,15 +16985,63 @@
         <v>2394</v>
       </c>
       <c r="B1185" t="s" s="2">
-        <v>2394</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="s" s="2">
-        <v>2395</v>
+        <v>2396</v>
       </c>
       <c r="B1186" t="s" s="2">
-        <v>2396</v>
+        <v>2397</v>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="s" s="2">
+        <v>2398</v>
+      </c>
+      <c r="B1187" t="s" s="2">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="s" s="2">
+        <v>2400</v>
+      </c>
+      <c r="B1188" t="s" s="2">
+        <v>2401</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="s" s="2">
+        <v>2402</v>
+      </c>
+      <c r="B1189" t="s" s="2">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="s" s="2">
+        <v>2404</v>
+      </c>
+      <c r="B1190" t="s" s="2">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="s" s="2">
+        <v>2406</v>
+      </c>
+      <c r="B1191" t="s" s="2">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="s" s="2">
+        <v>2407</v>
+      </c>
+      <c r="B1192" t="s" s="2">
+        <v>2408</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="2409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2423" uniqueCount="2421">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250919120000</t>
+    <t>20251017120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-19T12:00:00+01:00</t>
+    <t>2025-10-17T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -7231,6 +7231,42 @@
   </si>
   <si>
     <t>Autodialyse assistée</t>
+  </si>
+  <si>
+    <t>1551</t>
+  </si>
+  <si>
+    <t>Accueil en unité protégée</t>
+  </si>
+  <si>
+    <t>1552</t>
+  </si>
+  <si>
+    <t>Rééducation par réalité virtuelle</t>
+  </si>
+  <si>
+    <t>1553</t>
+  </si>
+  <si>
+    <t>Rééducation de l’amputé</t>
+  </si>
+  <si>
+    <t>1554</t>
+  </si>
+  <si>
+    <t>Rééducation vestibulaire (trouble de l’équilibre)</t>
+  </si>
+  <si>
+    <t>1555</t>
+  </si>
+  <si>
+    <t>Rééducation du rachis</t>
+  </si>
+  <si>
+    <t>1556</t>
+  </si>
+  <si>
+    <t>Rééducation des paralysies cérébrales et polyhandicaps</t>
   </si>
   <si>
     <t/>
@@ -7501,7 +7537,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1192"/>
+  <dimension ref="A1:B1198"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -17033,15 +17069,63 @@
         <v>2406</v>
       </c>
       <c r="B1191" t="s" s="2">
-        <v>2406</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="s" s="2">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="B1192" t="s" s="2">
-        <v>2408</v>
+        <v>2409</v>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="s" s="2">
+        <v>2410</v>
+      </c>
+      <c r="B1193" t="s" s="2">
+        <v>2411</v>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="s" s="2">
+        <v>2412</v>
+      </c>
+      <c r="B1194" t="s" s="2">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="s" s="2">
+        <v>2414</v>
+      </c>
+      <c r="B1195" t="s" s="2">
+        <v>2415</v>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="s" s="2">
+        <v>2416</v>
+      </c>
+      <c r="B1196" t="s" s="2">
+        <v>2417</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="s" s="2">
+        <v>2418</v>
+      </c>
+      <c r="B1197" t="s" s="2">
+        <v>2418</v>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="s" s="2">
+        <v>2419</v>
+      </c>
+      <c r="B1198" t="s" s="2">
+        <v>2420</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2423" uniqueCount="2421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2457" uniqueCount="2455">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251017120000</t>
+    <t>20251222120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-17T12:00:00+01:00</t>
+    <t>2025-12-22T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1782,13 +1782,13 @@
     <t>0523</t>
   </si>
   <si>
-    <t>Sevrage simple</t>
+    <t>Sevrage à faible risque de complication médicale (sevrage simple)</t>
   </si>
   <si>
     <t>0524</t>
   </si>
   <si>
-    <t>Sevrage complexe</t>
+    <t>Sevrage à fort risque de complication médicale (sevrage complexe)</t>
   </si>
   <si>
     <t>0525</t>
@@ -3402,13 +3402,13 @@
     <t>0849</t>
   </si>
   <si>
-    <t>Suivi cardiologique avec organisation de la prise en charge</t>
+    <t>Coordination pour assurer le suivi cardiologique avec organisation de la prise en charge</t>
   </si>
   <si>
     <t>0850</t>
   </si>
   <si>
-    <t>Suivi gynécologique avec organisation de la prise en charge</t>
+    <t>Coordination pour assurer le suivi gynécologique avec organisation de la prise en charge</t>
   </si>
   <si>
     <t>0851</t>
@@ -3474,7 +3474,7 @@
     <t>0861</t>
   </si>
   <si>
-    <t>Dépistage et suivi des pathologies endocriniennes</t>
+    <t>Dépistage et suivi biologique des pathologies endocriniennes</t>
   </si>
   <si>
     <t>0862</t>
@@ -3609,12 +3609,6 @@
     <t>Soins permanents continus par délégation / Présence aide-soignant de nuit</t>
   </si>
   <si>
-    <t>0887</t>
-  </si>
-  <si>
-    <t>Chirurgie sénologique</t>
-  </si>
-  <si>
     <t>0888</t>
   </si>
   <si>
@@ -3858,13 +3852,13 @@
     <t>0965</t>
   </si>
   <si>
-    <t>Réadaptation du cancer du sein</t>
+    <t>Rééducation du cancer du sein</t>
   </si>
   <si>
     <t>0966</t>
   </si>
   <si>
-    <t>Réadaptation des cicatrices</t>
+    <t>Rééducation des cicatrices</t>
   </si>
   <si>
     <t>0967</t>
@@ -3876,7 +3870,7 @@
     <t>0968</t>
   </si>
   <si>
-    <t>Réadaptation de la main</t>
+    <t>Rééducation de la main</t>
   </si>
   <si>
     <t>0969</t>
@@ -3900,7 +3894,7 @@
     <t>0972</t>
   </si>
   <si>
-    <t>Réadaptation maxillo-faciale</t>
+    <t>Rééducation maxillo-faciale</t>
   </si>
   <si>
     <t>0973</t>
@@ -3912,7 +3906,7 @@
     <t>0974</t>
   </si>
   <si>
-    <t>Réadaptation de la Mucoviscidose</t>
+    <t>Rééducation de la Mucoviscidose</t>
   </si>
   <si>
     <t>0975</t>
@@ -4146,7 +4140,7 @@
     <t>1013</t>
   </si>
   <si>
-    <t>Vaccination contre les infections sexuellement transmissible (IST)</t>
+    <t>Vaccination contre les infections sexuellement transmissibles (IST)</t>
   </si>
   <si>
     <t>1014</t>
@@ -4860,7 +4854,7 @@
     <t>1135</t>
   </si>
   <si>
-    <t>Angio IRM cérébral</t>
+    <t>Angio IRM cérébrale</t>
   </si>
   <si>
     <t>1136</t>
@@ -5184,7 +5178,7 @@
     <t>1191</t>
   </si>
   <si>
-    <t>Embolisation cérébrale anévrisme MAV</t>
+    <t>Embolisation cérébrale anévrisme Malformation Antéro Veineuse (MAV)</t>
   </si>
   <si>
     <t>1192</t>
@@ -5352,7 +5346,7 @@
     <t>1220</t>
   </si>
   <si>
-    <t>IRM CAI et APC</t>
+    <t>IRM Conduit Auditif Interne (CAI) et Angle Ponto-Cérébelleux (APC)</t>
   </si>
   <si>
     <t>1221</t>
@@ -5604,7 +5598,7 @@
     <t>1262</t>
   </si>
   <si>
-    <t>Scanner pré TAVI</t>
+    <t>Scanner pré Implantation d'une valve aortique par voie percutanée (TAVI)</t>
   </si>
   <si>
     <t>1263</t>
@@ -6666,7 +6660,7 @@
     <t>1454</t>
   </si>
   <si>
-    <t>Evaluation et suivi standardisé clinique et paraclinique des commotions cérébrales (Traumatisme Crânien Léger - TCL)</t>
+    <t>Evaluation et suivi standardisé clinique et paraclinique des commotions cérébrales (Traumatisme Crânien Léger - TCL) dans un cadre sportif</t>
   </si>
   <si>
     <t>1455</t>
@@ -6738,7 +6732,7 @@
     <t>1467</t>
   </si>
   <si>
-    <t>Examen visuel du sportif</t>
+    <t>Evaluation de la vue du sportif</t>
   </si>
   <si>
     <t>1468</t>
@@ -6798,19 +6792,19 @@
     <t>1478</t>
   </si>
   <si>
-    <t>Réadaptation des migraines et céphalées</t>
+    <t>Rééducation des migraines et céphalées</t>
   </si>
   <si>
     <t>1479</t>
   </si>
   <si>
-    <t>Réadaptation abdominale du post partum</t>
+    <t>Rééducation abdominale du post partum</t>
   </si>
   <si>
     <t>1480</t>
   </si>
   <si>
-    <t>Réadaptation abdominale préopératoire et post opératoire</t>
+    <t>Rééducation abdominale préopératoire et post opératoire</t>
   </si>
   <si>
     <t>1481</t>
@@ -7267,6 +7261,114 @@
   </si>
   <si>
     <t>Rééducation des paralysies cérébrales et polyhandicaps</t>
+  </si>
+  <si>
+    <t>1557</t>
+  </si>
+  <si>
+    <t>Prise en charge de bébé grand prématuré (&lt; 28 SA)</t>
+  </si>
+  <si>
+    <t>1558</t>
+  </si>
+  <si>
+    <t>Veille sanitaire et analyse de produit in situ</t>
+  </si>
+  <si>
+    <t>1559</t>
+  </si>
+  <si>
+    <t>Evaluation et suivi des addictions liées au cannabis et cannabinoïdes</t>
+  </si>
+  <si>
+    <t>1560</t>
+  </si>
+  <si>
+    <t>Evaluation et suivi des addictions liées aux psychostimulants (cocaïne, crack, dérivés des amphétamines, ecstasy, MDMA, cathinones de synthèse…)</t>
+  </si>
+  <si>
+    <t>1561</t>
+  </si>
+  <si>
+    <t>Evaluation et suivi des addictions liées aux opiacés (héroïne, morphinique)</t>
+  </si>
+  <si>
+    <t>1562</t>
+  </si>
+  <si>
+    <t>Evaluation et suivi des addictions liées aux autres substances (hallucinogènes, champignons, LSD, kétamine)</t>
+  </si>
+  <si>
+    <t>1563</t>
+  </si>
+  <si>
+    <t>Evaluation et suivi des addictions liées aux benzodiazépines et autres sédatifs</t>
+  </si>
+  <si>
+    <t>1564</t>
+  </si>
+  <si>
+    <t>Evaluation et suivi des addictions liées au chemsex (cathinones de synthèse, poppers, etc)</t>
+  </si>
+  <si>
+    <t>1570</t>
+  </si>
+  <si>
+    <t>Rééducation vésico-sphinctérienne</t>
+  </si>
+  <si>
+    <t>1571</t>
+  </si>
+  <si>
+    <t>Rééducation anorectale</t>
+  </si>
+  <si>
+    <t>1572</t>
+  </si>
+  <si>
+    <t>Rééducation des troubles de la déglutition</t>
+  </si>
+  <si>
+    <t>1573</t>
+  </si>
+  <si>
+    <t>Rééducation post-COVID (COVID long)</t>
+  </si>
+  <si>
+    <t>1574</t>
+  </si>
+  <si>
+    <t>Centre Ressources Autisme (CRA)</t>
+  </si>
+  <si>
+    <t>1575</t>
+  </si>
+  <si>
+    <t>Centre de référence des Troubles du Langage et de l’Apprentissage (CRTLA)</t>
+  </si>
+  <si>
+    <t>1576</t>
+  </si>
+  <si>
+    <t>Centre de référence du Trouble Déficit de l’Attention avec ou sans Hyperactivité (CRTDAH)</t>
+  </si>
+  <si>
+    <t>1577</t>
+  </si>
+  <si>
+    <t>Centre de compétence centre mémoire ressources et recherche (CMRR)</t>
+  </si>
+  <si>
+    <t>1578</t>
+  </si>
+  <si>
+    <t>Centre expert Parkinson</t>
+  </si>
+  <si>
+    <t>1579</t>
+  </si>
+  <si>
+    <t>Centre de ressources et de compétences sclérose en plaques (SEP)</t>
   </si>
   <si>
     <t/>
@@ -7537,7 +7639,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1198"/>
+  <dimension ref="A1:B1215"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -17117,15 +17219,151 @@
         <v>2418</v>
       </c>
       <c r="B1197" t="s" s="2">
-        <v>2418</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="s" s="2">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="B1198" t="s" s="2">
-        <v>2420</v>
+        <v>2421</v>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="s" s="2">
+        <v>2422</v>
+      </c>
+      <c r="B1199" t="s" s="2">
+        <v>2423</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="s" s="2">
+        <v>2424</v>
+      </c>
+      <c r="B1200" t="s" s="2">
+        <v>2425</v>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="s" s="2">
+        <v>2426</v>
+      </c>
+      <c r="B1201" t="s" s="2">
+        <v>2427</v>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="s" s="2">
+        <v>2428</v>
+      </c>
+      <c r="B1202" t="s" s="2">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="s" s="2">
+        <v>2430</v>
+      </c>
+      <c r="B1203" t="s" s="2">
+        <v>2431</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="s" s="2">
+        <v>2432</v>
+      </c>
+      <c r="B1204" t="s" s="2">
+        <v>2433</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="s" s="2">
+        <v>2434</v>
+      </c>
+      <c r="B1205" t="s" s="2">
+        <v>2435</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="s" s="2">
+        <v>2436</v>
+      </c>
+      <c r="B1206" t="s" s="2">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="s" s="2">
+        <v>2438</v>
+      </c>
+      <c r="B1207" t="s" s="2">
+        <v>2439</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="s" s="2">
+        <v>2440</v>
+      </c>
+      <c r="B1208" t="s" s="2">
+        <v>2441</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="s" s="2">
+        <v>2442</v>
+      </c>
+      <c r="B1209" t="s" s="2">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="s" s="2">
+        <v>2444</v>
+      </c>
+      <c r="B1210" t="s" s="2">
+        <v>2445</v>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="s" s="2">
+        <v>2446</v>
+      </c>
+      <c r="B1211" t="s" s="2">
+        <v>2447</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="s" s="2">
+        <v>2448</v>
+      </c>
+      <c r="B1212" t="s" s="2">
+        <v>2449</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="s" s="2">
+        <v>2450</v>
+      </c>
+      <c r="B1213" t="s" s="2">
+        <v>2451</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="s" s="2">
+        <v>2452</v>
+      </c>
+      <c r="B1214" t="s" s="2">
+        <v>2452</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="s" s="2">
+        <v>2453</v>
+      </c>
+      <c r="B1215" t="s" s="2">
+        <v>2454</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2457" uniqueCount="2455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2529" uniqueCount="2527">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -597,12 +597,6 @@
     <t>Contrepulsion par ballon intraaortique (CPBIA)</t>
   </si>
   <si>
-    <t>0145</t>
-  </si>
-  <si>
-    <t>Coronarographie</t>
-  </si>
-  <si>
     <t>0146</t>
   </si>
   <si>
@@ -1773,12 +1767,6 @@
     <t>Thoracoscopie</t>
   </si>
   <si>
-    <t>0522</t>
-  </si>
-  <si>
-    <t>Prise en charge de la tuberculose</t>
-  </si>
-  <si>
     <t>0523</t>
   </si>
   <si>
@@ -3192,7 +3180,7 @@
     <t>0814</t>
   </si>
   <si>
-    <t>Soutien et écoute téléphonique</t>
+    <t>Soutien et écoute à distance (par téléphone et/ou par messagerie)</t>
   </si>
   <si>
     <t>0815</t>
@@ -5031,12 +5019,6 @@
     <t>Chirurgie percutanée du rein</t>
   </si>
   <si>
-    <t>1165</t>
-  </si>
-  <si>
-    <t>Chirurgie proctologique</t>
-  </si>
-  <si>
     <t>1167</t>
   </si>
   <si>
@@ -5829,18 +5811,6 @@
     <t>Échographie de datation de grossesse</t>
   </si>
   <si>
-    <t>1302</t>
-  </si>
-  <si>
-    <t>Echographie de mesure de la clarté nucale par PS agréé</t>
-  </si>
-  <si>
-    <t>1303</t>
-  </si>
-  <si>
-    <t>Échographie morphologique du 2ème trimestre</t>
-  </si>
-  <si>
     <t>1304</t>
   </si>
   <si>
@@ -6342,7 +6312,7 @@
     <t>1391</t>
   </si>
   <si>
-    <t>Maladies vectorielles à tique (Lyme…)</t>
+    <t>Prise en charge de maladies vectorielles à tique (Lyme…)</t>
   </si>
   <si>
     <t>1392</t>
@@ -6654,7 +6624,7 @@
     <t>1453</t>
   </si>
   <si>
-    <t>Suivi, repérage précoce et accompagnement du développement psychomoteur, des troubles de comportement et des Troubles Neuro Développementaux</t>
+    <t>Suivi, repérage précoce et accompagnement du développement psychomoteur, des troubles de comportement et des Troubles Neuro Développementaux</t>
   </si>
   <si>
     <t>1454</t>
@@ -7311,6 +7281,36 @@
     <t>Evaluation et suivi des addictions liées au chemsex (cathinones de synthèse, poppers, etc)</t>
   </si>
   <si>
+    <t>1565</t>
+  </si>
+  <si>
+    <t>Groupe « entendeurs de voix » - hallucinations auditives</t>
+  </si>
+  <si>
+    <t>1566</t>
+  </si>
+  <si>
+    <t>Groupe directives anticipées en psychiatrie</t>
+  </si>
+  <si>
+    <t>1567</t>
+  </si>
+  <si>
+    <t>Autodétermination par la participation des adhérents à la gestion de la structure</t>
+  </si>
+  <si>
+    <t>1568</t>
+  </si>
+  <si>
+    <t>Activités sociales, culturelles, sportives et de loisirs</t>
+  </si>
+  <si>
+    <t>1569</t>
+  </si>
+  <si>
+    <t>Dépôt de plainte sur site</t>
+  </si>
+  <si>
     <t>1570</t>
   </si>
   <si>
@@ -7369,6 +7369,222 @@
   </si>
   <si>
     <t>Centre de ressources et de compétences sclérose en plaques (SEP)</t>
+  </si>
+  <si>
+    <t>1580</t>
+  </si>
+  <si>
+    <t>Relayage courte durée (quelques heures par jour)</t>
+  </si>
+  <si>
+    <t>1581</t>
+  </si>
+  <si>
+    <t>Relayage longue durée (sur plusieurs jours)</t>
+  </si>
+  <si>
+    <t>1582</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en cardiologie</t>
+  </si>
+  <si>
+    <t>1583</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie cardiaque et gros vaisseaux</t>
+  </si>
+  <si>
+    <t>1584</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie digestive et viscérale</t>
+  </si>
+  <si>
+    <t>1585</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie maxillo-faciale et stomatologie</t>
+  </si>
+  <si>
+    <t>1586</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie orthopédique et traumatologie</t>
+  </si>
+  <si>
+    <t>1587</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie pédiatrique orthopédique et traumatologie</t>
+  </si>
+  <si>
+    <t>1588</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie pédiatrique viscérale et digestive</t>
+  </si>
+  <si>
+    <t>1589</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie thoracique et pulmonaire</t>
+  </si>
+  <si>
+    <t>1590</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie vasculaire</t>
+  </si>
+  <si>
+    <t>1591</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en dermatologie</t>
+  </si>
+  <si>
+    <t>1592</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en endocrinologie</t>
+  </si>
+  <si>
+    <t>1593</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en gériatrie (gérontologie)</t>
+  </si>
+  <si>
+    <t>1594</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en gynécologie</t>
+  </si>
+  <si>
+    <t>1595</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en hématologie</t>
+  </si>
+  <si>
+    <t>1596</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en hépato-gastro-entérologie</t>
+  </si>
+  <si>
+    <t>1597</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en maladies infectieuses et tropicales</t>
+  </si>
+  <si>
+    <t>1598</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en médecine interne</t>
+  </si>
+  <si>
+    <t>1599</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en médecine vasculaire</t>
+  </si>
+  <si>
+    <t>1600</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en néphrologie (dont dialyse)</t>
+  </si>
+  <si>
+    <t>1601</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en neurochirurgie</t>
+  </si>
+  <si>
+    <t>1602</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en neurologie</t>
+  </si>
+  <si>
+    <t>1603</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en oncologie</t>
+  </si>
+  <si>
+    <t>1604</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en ophtalmologie</t>
+  </si>
+  <si>
+    <t>1605</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en oto-rhino-laryngologie (ORL) et chirurgie cervico-faciale</t>
+  </si>
+  <si>
+    <t>1606</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en pédiatrie</t>
+  </si>
+  <si>
+    <t>1607</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en pneumologie</t>
+  </si>
+  <si>
+    <t>1608</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en rhumatologie</t>
+  </si>
+  <si>
+    <t>1609</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en urologie</t>
+  </si>
+  <si>
+    <t>1610</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en caisson oxygène hyperbare</t>
+  </si>
+  <si>
+    <t>1611</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie de la main SOS main</t>
+  </si>
+  <si>
+    <t>1612</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en odontologie</t>
+  </si>
+  <si>
+    <t>1613</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en psychiatrie (dont équipe de liaison)</t>
+  </si>
+  <si>
+    <t>1614</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en radiologie interventionnelle</t>
+  </si>
+  <si>
+    <t>1615</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) rachis</t>
   </si>
   <si>
     <t/>
@@ -7639,7 +7855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1215"/>
+  <dimension ref="A1:B1251"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -17355,15 +17571,303 @@
         <v>2452</v>
       </c>
       <c r="B1214" t="s" s="2">
-        <v>2452</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="1215">
       <c r="A1215" t="s" s="2">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="B1215" t="s" s="2">
-        <v>2454</v>
+        <v>2455</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="s" s="2">
+        <v>2456</v>
+      </c>
+      <c r="B1216" t="s" s="2">
+        <v>2457</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="s" s="2">
+        <v>2458</v>
+      </c>
+      <c r="B1217" t="s" s="2">
+        <v>2459</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="s" s="2">
+        <v>2460</v>
+      </c>
+      <c r="B1218" t="s" s="2">
+        <v>2461</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="s" s="2">
+        <v>2462</v>
+      </c>
+      <c r="B1219" t="s" s="2">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="s" s="2">
+        <v>2464</v>
+      </c>
+      <c r="B1220" t="s" s="2">
+        <v>2465</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="s" s="2">
+        <v>2466</v>
+      </c>
+      <c r="B1221" t="s" s="2">
+        <v>2467</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="s" s="2">
+        <v>2468</v>
+      </c>
+      <c r="B1222" t="s" s="2">
+        <v>2469</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="s" s="2">
+        <v>2470</v>
+      </c>
+      <c r="B1223" t="s" s="2">
+        <v>2471</v>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="s" s="2">
+        <v>2472</v>
+      </c>
+      <c r="B1224" t="s" s="2">
+        <v>2473</v>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="s" s="2">
+        <v>2474</v>
+      </c>
+      <c r="B1225" t="s" s="2">
+        <v>2475</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="s" s="2">
+        <v>2476</v>
+      </c>
+      <c r="B1226" t="s" s="2">
+        <v>2477</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="s" s="2">
+        <v>2478</v>
+      </c>
+      <c r="B1227" t="s" s="2">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="s" s="2">
+        <v>2480</v>
+      </c>
+      <c r="B1228" t="s" s="2">
+        <v>2481</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="s" s="2">
+        <v>2482</v>
+      </c>
+      <c r="B1229" t="s" s="2">
+        <v>2483</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="s" s="2">
+        <v>2484</v>
+      </c>
+      <c r="B1230" t="s" s="2">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="s" s="2">
+        <v>2486</v>
+      </c>
+      <c r="B1231" t="s" s="2">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="s" s="2">
+        <v>2488</v>
+      </c>
+      <c r="B1232" t="s" s="2">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="s" s="2">
+        <v>2490</v>
+      </c>
+      <c r="B1233" t="s" s="2">
+        <v>2491</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="s" s="2">
+        <v>2492</v>
+      </c>
+      <c r="B1234" t="s" s="2">
+        <v>2493</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="s" s="2">
+        <v>2494</v>
+      </c>
+      <c r="B1235" t="s" s="2">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="s" s="2">
+        <v>2496</v>
+      </c>
+      <c r="B1236" t="s" s="2">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="s" s="2">
+        <v>2498</v>
+      </c>
+      <c r="B1237" t="s" s="2">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="s" s="2">
+        <v>2500</v>
+      </c>
+      <c r="B1238" t="s" s="2">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="s" s="2">
+        <v>2502</v>
+      </c>
+      <c r="B1239" t="s" s="2">
+        <v>2503</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="s" s="2">
+        <v>2504</v>
+      </c>
+      <c r="B1240" t="s" s="2">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="s" s="2">
+        <v>2506</v>
+      </c>
+      <c r="B1241" t="s" s="2">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="s" s="2">
+        <v>2508</v>
+      </c>
+      <c r="B1242" t="s" s="2">
+        <v>2509</v>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="s" s="2">
+        <v>2510</v>
+      </c>
+      <c r="B1243" t="s" s="2">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="s" s="2">
+        <v>2512</v>
+      </c>
+      <c r="B1244" t="s" s="2">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="s" s="2">
+        <v>2514</v>
+      </c>
+      <c r="B1245" t="s" s="2">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="s" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B1246" t="s" s="2">
+        <v>2517</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="s" s="2">
+        <v>2518</v>
+      </c>
+      <c r="B1247" t="s" s="2">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="s" s="2">
+        <v>2520</v>
+      </c>
+      <c r="B1248" t="s" s="2">
+        <v>2521</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="s" s="2">
+        <v>2522</v>
+      </c>
+      <c r="B1249" t="s" s="2">
+        <v>2523</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="s" s="2">
+        <v>2524</v>
+      </c>
+      <c r="B1250" t="s" s="2">
+        <v>2524</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="s" s="2">
+        <v>2525</v>
+      </c>
+      <c r="B1251" t="s" s="2">
+        <v>2526</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2529" uniqueCount="2527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2561" uniqueCount="2559">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260601120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00+01:00</t>
+    <t>2026-06-01T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1842,7 +1842,7 @@
     <t>0538</t>
   </si>
   <si>
-    <t>Thérapie de groupe ou atelier à médiation orale et-ou écrite (groupe de parole, d'écriture)</t>
+    <t>Thérapie de groupe ou atelier à médiation orale et/ou écrite (groupe de parole, d'écriture)</t>
   </si>
   <si>
     <t>0539</t>
@@ -4134,7 +4134,7 @@
     <t>1014</t>
   </si>
   <si>
-    <t>Fourniture de matériel d'hygiène, de prévention et de RdRD</t>
+    <t>Fourniture de matériel d’hygiène, de prévention et de Réduction des Risques et des Dommages (RdRD)</t>
   </si>
   <si>
     <t>1015</t>
@@ -6624,7 +6624,7 @@
     <t>1453</t>
   </si>
   <si>
-    <t>Suivi, repérage précoce et accompagnement du développement psychomoteur, des troubles de comportement et des Troubles Neuro Développementaux</t>
+    <t>Suivi, repérage précoce et accompagnement du développement psychomoteur, des troubles de comportement et des Troubles Neuro Développementaux</t>
   </si>
   <si>
     <t>1454</t>
@@ -7386,205 +7386,301 @@
     <t>1582</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en cardiologie</t>
+    <t>Prise en charge spécialisée et continue en cardiologie</t>
   </si>
   <si>
     <t>1583</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie cardiaque et gros vaisseaux</t>
+    <t>Prise en charge spécialisée et continue en chirurgie cardiaque et gros vaisseaux</t>
   </si>
   <si>
     <t>1584</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie digestive et viscérale</t>
+    <t>Prise en charge spécialisée et continue en chirurgie digestive et viscérale</t>
   </si>
   <si>
     <t>1585</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie maxillo-faciale et stomatologie</t>
+    <t>Prise en charge spécialisée et continue en chirurgie maxillo-faciale et stomatologie</t>
   </si>
   <si>
     <t>1586</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie orthopédique et traumatologie</t>
+    <t>Prise en charge spécialisée et continue en chirurgie orthopédique et traumatologie</t>
   </si>
   <si>
     <t>1587</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie pédiatrique orthopédique et traumatologie</t>
+    <t>Prise en charge spécialisée et continue en chirurgie pédiatrique orthopédique et traumatologie</t>
   </si>
   <si>
     <t>1588</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie pédiatrique viscérale et digestive</t>
+    <t>Prise en charge spécialisée et continue en chirurgie pédiatrique viscérale et digestive</t>
   </si>
   <si>
     <t>1589</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie thoracique et pulmonaire</t>
+    <t>Prise en charge spécialisée et continue en chirurgie thoracique et pulmonaire</t>
   </si>
   <si>
     <t>1590</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie vasculaire</t>
+    <t>Prise en charge spécialisée et continue en chirurgie vasculaire</t>
   </si>
   <si>
     <t>1591</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en dermatologie</t>
+    <t>Prise en charge spécialisée et continue en dermatologie</t>
   </si>
   <si>
     <t>1592</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en endocrinologie</t>
+    <t>Prise en charge spécialisée et continue en endocrinologie</t>
   </si>
   <si>
     <t>1593</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en gériatrie (gérontologie)</t>
+    <t>Prise en charge spécialisée et continue en gériatrie (gérontologie)</t>
   </si>
   <si>
     <t>1594</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en gynécologie</t>
+    <t>Prise en charge spécialisée et continue en gynécologie</t>
   </si>
   <si>
     <t>1595</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en hématologie</t>
+    <t>Prise en charge spécialisée et continue en hématologie</t>
   </si>
   <si>
     <t>1596</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en hépato-gastro-entérologie</t>
+    <t>Prise en charge spécialisée et continue en hépato-gastro-entérologie</t>
   </si>
   <si>
     <t>1597</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en maladies infectieuses et tropicales</t>
+    <t>Prise en charge spécialisée et continue en maladies infectieuses et tropicales</t>
   </si>
   <si>
     <t>1598</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en médecine interne</t>
+    <t>Prise en charge spécialisée et continue en médecine interne</t>
   </si>
   <si>
     <t>1599</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en médecine vasculaire</t>
+    <t>Prise en charge spécialisée et continue en médecine vasculaire</t>
   </si>
   <si>
     <t>1600</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en néphrologie (dont dialyse)</t>
+    <t>Prise en charge spécialisée et continue en néphrologie (dont dialyse)</t>
   </si>
   <si>
     <t>1601</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en neurochirurgie</t>
+    <t>Prise en charge spécialisée et continue en neurochirurgie</t>
   </si>
   <si>
     <t>1602</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en neurologie</t>
+    <t>Prise en charge spécialisée et continue en neurologie</t>
   </si>
   <si>
     <t>1603</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en oncologie</t>
+    <t>Prise en charge spécialisée et continue en oncologie</t>
   </si>
   <si>
     <t>1604</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en ophtalmologie</t>
+    <t>Prise en charge spécialisée et continue en ophtalmologie</t>
   </si>
   <si>
     <t>1605</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en oto-rhino-laryngologie (ORL) et chirurgie cervico-faciale</t>
+    <t>Prise en charge spécialisée et continue en oto-rhino-laryngologie (ORL) et chirurgie cervico-faciale</t>
   </si>
   <si>
     <t>1606</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en pédiatrie</t>
+    <t>Prise en charge spécialisée et continue en pédiatrie</t>
   </si>
   <si>
     <t>1607</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en pneumologie</t>
+    <t>Prise en charge spécialisée et continue en pneumologie</t>
   </si>
   <si>
     <t>1608</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en rhumatologie</t>
+    <t>Prise en charge spécialisée et continue en rhumatologie</t>
   </si>
   <si>
     <t>1609</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en urologie</t>
+    <t>Prise en charge spécialisée et continue en urologie</t>
   </si>
   <si>
     <t>1610</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en caisson oxygène hyperbare</t>
+    <t>Prise en charge spécialisée et continue en caisson oxygène hyperbare</t>
   </si>
   <si>
     <t>1611</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie de la main SOS main</t>
+    <t>Prise en charge spécialisée et continue en chirurgie de la main SOS main</t>
   </si>
   <si>
     <t>1612</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en odontologie</t>
+    <t>Prise en charge spécialisée et continue en odontologie</t>
   </si>
   <si>
     <t>1613</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en psychiatrie (dont équipe de liaison)</t>
+    <t>Prise en charge spécialisée et continue en psychiatrie (dont équipe de liaison)</t>
   </si>
   <si>
     <t>1614</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en radiologie interventionnelle</t>
+    <t>Prise en charge spécialisée et continue en radiologie interventionnelle</t>
   </si>
   <si>
     <t>1615</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) rachis</t>
+    <t>Prise en charge spécialisée et continue rachis</t>
+  </si>
+  <si>
+    <t>1616</t>
+  </si>
+  <si>
+    <t>Pédicurie-podologie conventionnée du pied diabétique de grade 2 et 3</t>
+  </si>
+  <si>
+    <t>1617</t>
+  </si>
+  <si>
+    <t>Pédicurie-podologie conventionnée soins de support oncologie</t>
+  </si>
+  <si>
+    <t>1618</t>
+  </si>
+  <si>
+    <t>Orthoplastie (appareillage d’orteil)</t>
+  </si>
+  <si>
+    <t>1619</t>
+  </si>
+  <si>
+    <t>Orthonyxie (appareillage d’ongle)</t>
+  </si>
+  <si>
+    <t>1620</t>
+  </si>
+  <si>
+    <t>Onychoplastie (reconstruction de l’ongle)</t>
+  </si>
+  <si>
+    <t>1621</t>
+  </si>
+  <si>
+    <t>Orthèse plantaire (semelle orthopédique)</t>
+  </si>
+  <si>
+    <t>1622</t>
+  </si>
+  <si>
+    <t>Bilan diagnostique podologique de la prévention de la chute</t>
+  </si>
+  <si>
+    <t>1623</t>
+  </si>
+  <si>
+    <t>Rééducation du pied (sous la cheville)</t>
+  </si>
+  <si>
+    <t>1624</t>
+  </si>
+  <si>
+    <t>Contention nocturne</t>
+  </si>
+  <si>
+    <t>1625</t>
+  </si>
+  <si>
+    <t>Soin de pédicurie</t>
+  </si>
+  <si>
+    <t>1626</t>
+  </si>
+  <si>
+    <t>Traitement de la verrue plantaire par azote liquide</t>
+  </si>
+  <si>
+    <t>1627</t>
+  </si>
+  <si>
+    <t>Traitement sans douleur de l’ongle incarné par phénolisation (protocole de coopération)</t>
+  </si>
+  <si>
+    <t>1628</t>
+  </si>
+  <si>
+    <t>Prélèvement unguéal pour analyse biologique (protocole de coopération)</t>
+  </si>
+  <si>
+    <t>1629</t>
+  </si>
+  <si>
+    <t>Confection de semelle de comblement en polyuréthane (PU) pour amputation partielle du pied</t>
+  </si>
+  <si>
+    <t>1630</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et continue en pédopsychiatrie (dont équipe de liaison)</t>
+  </si>
+  <si>
+    <t>1631</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et continue SOS main</t>
   </si>
   <si>
     <t/>
@@ -7855,7 +7951,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1251"/>
+  <dimension ref="A1:B1267"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -17859,15 +17955,143 @@
         <v>2524</v>
       </c>
       <c r="B1250" t="s" s="2">
-        <v>2524</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="1251">
       <c r="A1251" t="s" s="2">
-        <v>2525</v>
+        <v>2526</v>
       </c>
       <c r="B1251" t="s" s="2">
-        <v>2526</v>
+        <v>2527</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="s" s="2">
+        <v>2528</v>
+      </c>
+      <c r="B1252" t="s" s="2">
+        <v>2529</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="s" s="2">
+        <v>2530</v>
+      </c>
+      <c r="B1253" t="s" s="2">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="s" s="2">
+        <v>2532</v>
+      </c>
+      <c r="B1254" t="s" s="2">
+        <v>2533</v>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="s" s="2">
+        <v>2534</v>
+      </c>
+      <c r="B1255" t="s" s="2">
+        <v>2535</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="s" s="2">
+        <v>2536</v>
+      </c>
+      <c r="B1256" t="s" s="2">
+        <v>2537</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="s" s="2">
+        <v>2538</v>
+      </c>
+      <c r="B1257" t="s" s="2">
+        <v>2539</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="s" s="2">
+        <v>2540</v>
+      </c>
+      <c r="B1258" t="s" s="2">
+        <v>2541</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="s" s="2">
+        <v>2542</v>
+      </c>
+      <c r="B1259" t="s" s="2">
+        <v>2543</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="s" s="2">
+        <v>2544</v>
+      </c>
+      <c r="B1260" t="s" s="2">
+        <v>2545</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="s" s="2">
+        <v>2546</v>
+      </c>
+      <c r="B1261" t="s" s="2">
+        <v>2547</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="s" s="2">
+        <v>2548</v>
+      </c>
+      <c r="B1262" t="s" s="2">
+        <v>2549</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="s" s="2">
+        <v>2550</v>
+      </c>
+      <c r="B1263" t="s" s="2">
+        <v>2551</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="s" s="2">
+        <v>2552</v>
+      </c>
+      <c r="B1264" t="s" s="2">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="s" s="2">
+        <v>2554</v>
+      </c>
+      <c r="B1265" t="s" s="2">
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="s" s="2">
+        <v>2556</v>
+      </c>
+      <c r="B1266" t="s" s="2">
+        <v>2556</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="s" s="2">
+        <v>2557</v>
+      </c>
+      <c r="B1267" t="s" s="2">
+        <v>2558</v>
       </c>
     </row>
   </sheetData>
